--- a/KoF/2026_KoF_Result.xlsx
+++ b/KoF/2026_KoF_Result.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83462144-B756-40DA-8D2F-203D676EB158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87EB77BA-C7F1-4908-942B-E49CD801DAB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{521ED91F-5C26-4B0E-8403-9E93154C70E8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{521ED91F-5C26-4B0E-8403-9E93154C70E8}"/>
   </bookViews>
   <sheets>
     <sheet name="Guide" sheetId="9" r:id="rId1"/>
@@ -1111,7 +1111,22 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="16" fontId="12" fillId="7" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1121,21 +1136,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2429,15 +2429,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" s="15" customFormat="1" ht="19.2" x14ac:dyDescent="0.35">
-      <c r="B1" s="67" t="s">
+      <c r="B1" s="72" t="s">
         <v>74</v>
       </c>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
       <c r="I1" s="22"/>
       <c r="J1" s="14"/>
       <c r="K1" s="22"/>
@@ -2463,157 +2463,157 @@
     <row r="2" spans="1:33" ht="19.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="16"/>
       <c r="C2" s="16"/>
-      <c r="D2" s="64">
+      <c r="D2" s="68">
         <v>1</v>
       </c>
-      <c r="E2" s="64"/>
-      <c r="F2" s="64">
+      <c r="E2" s="68"/>
+      <c r="F2" s="68">
         <v>2</v>
       </c>
-      <c r="G2" s="64"/>
-      <c r="H2" s="64">
+      <c r="G2" s="68"/>
+      <c r="H2" s="68">
         <v>3</v>
       </c>
-      <c r="I2" s="64"/>
-      <c r="J2" s="72">
+      <c r="I2" s="68"/>
+      <c r="J2" s="69">
         <v>4</v>
       </c>
-      <c r="K2" s="72"/>
-      <c r="L2" s="64">
+      <c r="K2" s="69"/>
+      <c r="L2" s="68">
         <v>5</v>
       </c>
-      <c r="M2" s="64"/>
-      <c r="N2" s="64">
+      <c r="M2" s="68"/>
+      <c r="N2" s="68">
         <v>6</v>
       </c>
-      <c r="O2" s="64"/>
-      <c r="P2" s="64">
+      <c r="O2" s="68"/>
+      <c r="P2" s="68">
         <v>7</v>
       </c>
-      <c r="Q2" s="64"/>
-      <c r="R2" s="64">
+      <c r="Q2" s="68"/>
+      <c r="R2" s="68">
         <v>8</v>
       </c>
-      <c r="S2" s="64"/>
-      <c r="T2" s="64">
+      <c r="S2" s="68"/>
+      <c r="T2" s="68">
         <v>9</v>
       </c>
-      <c r="U2" s="64"/>
-      <c r="V2" s="64">
+      <c r="U2" s="68"/>
+      <c r="V2" s="68">
         <v>10</v>
       </c>
-      <c r="W2" s="64"/>
-      <c r="X2" s="64">
+      <c r="W2" s="68"/>
+      <c r="X2" s="68">
         <v>11</v>
       </c>
-      <c r="Y2" s="64"/>
-      <c r="Z2" s="64">
+      <c r="Y2" s="68"/>
+      <c r="Z2" s="68">
         <v>12</v>
       </c>
-      <c r="AA2" s="64"/>
-      <c r="AB2" s="64">
+      <c r="AA2" s="68"/>
+      <c r="AB2" s="68">
         <v>13</v>
       </c>
-      <c r="AC2" s="64"/>
-      <c r="AD2" s="64">
+      <c r="AC2" s="68"/>
+      <c r="AD2" s="68">
         <v>14</v>
       </c>
-      <c r="AE2" s="64"/>
-      <c r="AF2" s="64">
+      <c r="AE2" s="68"/>
+      <c r="AF2" s="68">
         <v>15</v>
       </c>
-      <c r="AG2" s="64"/>
+      <c r="AG2" s="68"/>
     </row>
     <row r="3" spans="1:33" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="70" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="68" t="s">
+      <c r="A3" s="64" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="66" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="68" t="s">
+      <c r="C3" s="66" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="66">
+      <c r="D3" s="71">
         <f>_xlfn.XLOOKUP(D2,Resultat!E4:S4,Resultat!E1:S1,"",0)</f>
         <v>46023</v>
       </c>
-      <c r="E3" s="66"/>
-      <c r="F3" s="66">
+      <c r="E3" s="71"/>
+      <c r="F3" s="71">
         <f>_xlfn.XLOOKUP(F2,Resultat!E4:S4,Resultat!E1:S1,"",0)</f>
         <v>46093</v>
       </c>
-      <c r="G3" s="66"/>
-      <c r="H3" s="66">
+      <c r="G3" s="71"/>
+      <c r="H3" s="71">
         <f>_xlfn.XLOOKUP(H2,Resultat!E4:S4,Resultat!E1:S1,"",0)</f>
         <v>46110</v>
       </c>
-      <c r="I3" s="66"/>
-      <c r="J3" s="65">
+      <c r="I3" s="71"/>
+      <c r="J3" s="70">
         <f>_xlfn.XLOOKUP(J2,Resultat!E4:S4,Resultat!E1:S1,"",0)</f>
         <v>46116</v>
       </c>
-      <c r="K3" s="65"/>
-      <c r="L3" s="66">
+      <c r="K3" s="70"/>
+      <c r="L3" s="71">
         <f>_xlfn.XLOOKUP(L2,Resultat!E4:S4,Resultat!E1:S1,"",0)</f>
         <v>46137</v>
       </c>
-      <c r="M3" s="66"/>
-      <c r="N3" s="65" t="str">
+      <c r="M3" s="71"/>
+      <c r="N3" s="70" t="str">
         <f>_xlfn.XLOOKUP(N2,Resultat!E4:S4,Resultat!E1:S1,"",0)</f>
         <v/>
       </c>
-      <c r="O3" s="65"/>
-      <c r="P3" s="66" t="str">
+      <c r="O3" s="70"/>
+      <c r="P3" s="71" t="str">
         <f>_xlfn.XLOOKUP(P2,Resultat!E4:S4,Resultat!E1:S1,"",0)</f>
         <v/>
       </c>
-      <c r="Q3" s="66"/>
-      <c r="R3" s="65" t="str">
+      <c r="Q3" s="71"/>
+      <c r="R3" s="70" t="str">
         <f>_xlfn.XLOOKUP(R2,Resultat!E4:S4,Resultat!E1:S1,"",0)</f>
         <v/>
       </c>
-      <c r="S3" s="65"/>
-      <c r="T3" s="66" t="str">
+      <c r="S3" s="70"/>
+      <c r="T3" s="71" t="str">
         <f>_xlfn.XLOOKUP(T2,Resultat!E4:S4,Resultat!E1:S1,"",0)</f>
         <v/>
       </c>
-      <c r="U3" s="66"/>
-      <c r="V3" s="65" t="str">
+      <c r="U3" s="71"/>
+      <c r="V3" s="70" t="str">
         <f>_xlfn.XLOOKUP(V2,Resultat!E4:S4,Resultat!E1:S1,"",0)</f>
         <v/>
       </c>
-      <c r="W3" s="65"/>
-      <c r="X3" s="66" t="str">
+      <c r="W3" s="70"/>
+      <c r="X3" s="71" t="str">
         <f>_xlfn.XLOOKUP(X2,Resultat!E4:S4,Resultat!E1:S1,"",0)</f>
         <v/>
       </c>
-      <c r="Y3" s="66"/>
-      <c r="Z3" s="65" t="str">
+      <c r="Y3" s="71"/>
+      <c r="Z3" s="70" t="str">
         <f>_xlfn.XLOOKUP(Z2,Resultat!E4:S4,Resultat!E1:S1,"",0)</f>
         <v/>
       </c>
-      <c r="AA3" s="65"/>
-      <c r="AB3" s="66" t="str">
+      <c r="AA3" s="70"/>
+      <c r="AB3" s="71" t="str">
         <f>_xlfn.XLOOKUP(AB2,Resultat!E4:S4,Resultat!E1:S1,"",0)</f>
         <v/>
       </c>
-      <c r="AC3" s="66"/>
-      <c r="AD3" s="65" t="str">
+      <c r="AC3" s="71"/>
+      <c r="AD3" s="70" t="str">
         <f>_xlfn.XLOOKUP(AD2,Resultat!E4:S4,Resultat!E1:S1,"",0)</f>
         <v/>
       </c>
-      <c r="AE3" s="65"/>
-      <c r="AF3" s="66" t="str">
+      <c r="AE3" s="70"/>
+      <c r="AF3" s="71" t="str">
         <f>_xlfn.XLOOKUP(AF2,Resultat!E4:S4,Resultat!E1:S1,"",0)</f>
         <v/>
       </c>
-      <c r="AG3" s="66"/>
+      <c r="AG3" s="71"/>
     </row>
     <row r="4" spans="1:33" s="18" customFormat="1" ht="10.199999999999999" x14ac:dyDescent="0.2">
-      <c r="A4" s="71"/>
-      <c r="B4" s="69"/>
-      <c r="C4" s="69"/>
+      <c r="A4" s="65"/>
+      <c r="B4" s="67"/>
+      <c r="C4" s="67"/>
       <c r="D4" s="28" t="s">
         <v>55</v>
       </c>
@@ -7425,25 +7425,6 @@
     <sortCondition ref="B37:B57"/>
   </sortState>
   <mergeCells count="34">
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="R2:S2"/>
-    <mergeCell ref="T2:U2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
     <mergeCell ref="AD2:AE2"/>
     <mergeCell ref="AD3:AE3"/>
     <mergeCell ref="AF2:AG2"/>
@@ -7459,6 +7440,25 @@
     <mergeCell ref="X3:Y3"/>
     <mergeCell ref="Z3:AA3"/>
     <mergeCell ref="AB3:AC3"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="T2:U2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="N3:O3"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:AG39">
     <cfRule type="expression" dxfId="1" priority="1">
